--- a/watch_list.xlsx
+++ b/watch_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>股票名称</t>
   </si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t>300499</t>
+  </si>
+  <si>
+    <t>数据港</t>
+  </si>
+  <si>
+    <t>603881</t>
+  </si>
+  <si>
+    <t>数据中心</t>
   </si>
 </sst>
 </file>
@@ -1225,8 +1234,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.6153846153846" customWidth="1"/>
     <col min="2" max="2" width="13.1346153846154" customWidth="1"/>
@@ -1309,6 +1318,17 @@
         <v>12</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/watch_list.xlsx
+++ b/watch_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>股票名称</t>
   </si>
@@ -87,6 +87,21 @@
   </si>
   <si>
     <t>数据中心</t>
+  </si>
+  <si>
+    <t>西测测试</t>
+  </si>
+  <si>
+    <t>301306</t>
+  </si>
+  <si>
+    <t>商业航天</t>
+  </si>
+  <si>
+    <t>信维通信</t>
+  </si>
+  <si>
+    <t>300136</t>
   </si>
 </sst>
 </file>
@@ -1234,8 +1249,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.6153846153846" customWidth="1"/>
     <col min="2" max="2" width="13.1346153846154" customWidth="1"/>
@@ -1329,6 +1344,28 @@
         <v>19</v>
       </c>
     </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/watch_list.xlsx
+++ b/watch_list.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="16080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="watch_list" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,98 +27,843 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="269">
+  <si>
+    <t>股票代码</t>
+  </si>
   <si>
     <t>股票名称</t>
   </si>
   <si>
-    <t>股票代码</t>
+    <t>主题</t>
   </si>
   <si>
     <t>行业</t>
   </si>
   <si>
+    <t>主题强度</t>
+  </si>
+  <si>
+    <t>排名</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>300308</t>
+  </si>
+  <si>
+    <t>中际旭创</t>
+  </si>
+  <si>
+    <t>CPO</t>
+  </si>
+  <si>
+    <t>CPO:TOP1</t>
+  </si>
+  <si>
+    <t>manual:AI算力产业链</t>
+  </si>
+  <si>
+    <t>300502</t>
+  </si>
+  <si>
+    <t>新易盛</t>
+  </si>
+  <si>
+    <t>CPO:TOP2</t>
+  </si>
+  <si>
+    <t>300394</t>
+  </si>
+  <si>
+    <t>天孚通信</t>
+  </si>
+  <si>
+    <t>CPO:TOP3</t>
+  </si>
+  <si>
+    <t>000988</t>
+  </si>
+  <si>
+    <t>华工科技</t>
+  </si>
+  <si>
+    <t>CPO:TOP4</t>
+  </si>
+  <si>
+    <t>688195</t>
+  </si>
+  <si>
+    <t>腾景科技</t>
+  </si>
+  <si>
+    <t>OCS</t>
+  </si>
+  <si>
+    <t>OCS:TOP1</t>
+  </si>
+  <si>
+    <t>002222</t>
+  </si>
+  <si>
+    <t>福晶科技</t>
+  </si>
+  <si>
+    <t>OCS:TOP2</t>
+  </si>
+  <si>
+    <t>300620</t>
+  </si>
+  <si>
+    <t>光库科技</t>
+  </si>
+  <si>
+    <t>OCS:TOP3</t>
+  </si>
+  <si>
+    <t>688205</t>
+  </si>
+  <si>
+    <t>德科立</t>
+  </si>
+  <si>
+    <t>OCS:TOP4</t>
+  </si>
+  <si>
+    <t>688498</t>
+  </si>
+  <si>
+    <t>源杰科技</t>
+  </si>
+  <si>
+    <t>光芯片</t>
+  </si>
+  <si>
+    <t>光芯片:TOP1</t>
+  </si>
+  <si>
+    <t>688313</t>
+  </si>
+  <si>
     <t>仕佳光子</t>
   </si>
   <si>
-    <t>688313</t>
-  </si>
-  <si>
-    <t>光通信</t>
-  </si>
-  <si>
-    <t>东田微</t>
-  </si>
-  <si>
-    <t>301183</t>
-  </si>
-  <si>
-    <t>太辰光</t>
-  </si>
-  <si>
-    <t>300570</t>
-  </si>
-  <si>
-    <t>飞龙股份</t>
-  </si>
-  <si>
-    <t>002536</t>
+    <t>光芯片:TOP2</t>
+  </si>
+  <si>
+    <t>002281</t>
+  </si>
+  <si>
+    <t>光迅科技</t>
+  </si>
+  <si>
+    <t>光芯片:TOP3</t>
+  </si>
+  <si>
+    <t>688048</t>
+  </si>
+  <si>
+    <t>长光华芯</t>
+  </si>
+  <si>
+    <t>光芯片:TOP4</t>
+  </si>
+  <si>
+    <t>300476</t>
+  </si>
+  <si>
+    <t>胜宏科技</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>PCB:TOP1</t>
+  </si>
+  <si>
+    <t>002384</t>
+  </si>
+  <si>
+    <t>东山精密</t>
+  </si>
+  <si>
+    <t>PCB:TOP2</t>
+  </si>
+  <si>
+    <t>002916</t>
+  </si>
+  <si>
+    <t>深南电路</t>
+  </si>
+  <si>
+    <t>PCB:TOP3</t>
+  </si>
+  <si>
+    <t>002463</t>
+  </si>
+  <si>
+    <t>沪电股份</t>
+  </si>
+  <si>
+    <t>PCB:TOP4</t>
+  </si>
+  <si>
+    <t>601138</t>
+  </si>
+  <si>
+    <t>工业富联</t>
+  </si>
+  <si>
+    <t>AI服务器</t>
+  </si>
+  <si>
+    <t>AI服务器:TOP1</t>
+  </si>
+  <si>
+    <t>000977</t>
+  </si>
+  <si>
+    <t>浪潮信息</t>
+  </si>
+  <si>
+    <t>AI服务器:TOP2</t>
+  </si>
+  <si>
+    <t>000938</t>
+  </si>
+  <si>
+    <t>紫光股份</t>
+  </si>
+  <si>
+    <t>AI服务器:TOP3</t>
+  </si>
+  <si>
+    <t>603019</t>
+  </si>
+  <si>
+    <t>中科曙光</t>
+  </si>
+  <si>
+    <t>AI服务器 / 液冷</t>
+  </si>
+  <si>
+    <t>AI服务器:TOP4; 液冷:TOP3</t>
+  </si>
+  <si>
+    <t>688041</t>
+  </si>
+  <si>
+    <t>海光信息</t>
+  </si>
+  <si>
+    <t>AI芯片</t>
+  </si>
+  <si>
+    <t>AI芯片:TOP1</t>
+  </si>
+  <si>
+    <t>688256</t>
+  </si>
+  <si>
+    <t>寒武纪</t>
+  </si>
+  <si>
+    <t>AI芯片:TOP2</t>
+  </si>
+  <si>
+    <t>688802</t>
+  </si>
+  <si>
+    <t>沐曦股份-U</t>
+  </si>
+  <si>
+    <t>AI芯片:TOP3</t>
+  </si>
+  <si>
+    <t>manual:AI算力产业链; 原表:沐曦股份</t>
+  </si>
+  <si>
+    <t>688795</t>
+  </si>
+  <si>
+    <t>摩尔线程-U</t>
+  </si>
+  <si>
+    <t>AI芯片:TOP4</t>
+  </si>
+  <si>
+    <t>manual:AI算力产业链; 原表:摩尔线程</t>
+  </si>
+  <si>
+    <t>601869</t>
+  </si>
+  <si>
+    <t>长飞光纤</t>
+  </si>
+  <si>
+    <t>光纤光缆</t>
+  </si>
+  <si>
+    <t>光纤光缆:TOP1</t>
+  </si>
+  <si>
+    <t>600487</t>
+  </si>
+  <si>
+    <t>亨通光电</t>
+  </si>
+  <si>
+    <t>光纤光缆:TOP2</t>
+  </si>
+  <si>
+    <t>600522</t>
+  </si>
+  <si>
+    <t>中天科技</t>
+  </si>
+  <si>
+    <t>光纤光缆:TOP3</t>
+  </si>
+  <si>
+    <t>600498</t>
+  </si>
+  <si>
+    <t>烽火通信</t>
+  </si>
+  <si>
+    <t>光纤光缆:TOP4</t>
+  </si>
+  <si>
+    <t>001309</t>
+  </si>
+  <si>
+    <t>德明利</t>
+  </si>
+  <si>
+    <t>存储芯片</t>
+  </si>
+  <si>
+    <t>存储芯片:TOP1</t>
+  </si>
+  <si>
+    <t>603986</t>
+  </si>
+  <si>
+    <t>兆易创新</t>
+  </si>
+  <si>
+    <t>存储芯片:TOP2</t>
+  </si>
+  <si>
+    <t>688525</t>
+  </si>
+  <si>
+    <t>佰维存储</t>
+  </si>
+  <si>
+    <t>存储芯片:TOP3</t>
+  </si>
+  <si>
+    <t>301308</t>
+  </si>
+  <si>
+    <t>江波龙</t>
+  </si>
+  <si>
+    <t>存储芯片:TOP4</t>
+  </si>
+  <si>
+    <t>300757</t>
+  </si>
+  <si>
+    <t>罗博特科</t>
+  </si>
+  <si>
+    <t>光模块设备</t>
+  </si>
+  <si>
+    <t>光模块设备:TOP1</t>
+  </si>
+  <si>
+    <t>002957</t>
+  </si>
+  <si>
+    <t>科瑞技术</t>
+  </si>
+  <si>
+    <t>光模块设备:TOP2</t>
+  </si>
+  <si>
+    <t>002975</t>
+  </si>
+  <si>
+    <t>博杰股份</t>
+  </si>
+  <si>
+    <t>光模块设备:TOP3</t>
+  </si>
+  <si>
+    <t>688170</t>
+  </si>
+  <si>
+    <t>德龙激光</t>
+  </si>
+  <si>
+    <t>光模块设备:TOP4</t>
+  </si>
+  <si>
+    <t>002475</t>
+  </si>
+  <si>
+    <t>立讯精密</t>
+  </si>
+  <si>
+    <t>高速连接</t>
+  </si>
+  <si>
+    <t>高速连接:TOP1</t>
+  </si>
+  <si>
+    <t>300913</t>
+  </si>
+  <si>
+    <t>兆龙互连</t>
+  </si>
+  <si>
+    <t>高速连接:TOP2</t>
+  </si>
+  <si>
+    <t>002130</t>
+  </si>
+  <si>
+    <t>沃尔核材</t>
+  </si>
+  <si>
+    <t>高速连接:TOP3</t>
+  </si>
+  <si>
+    <t>688668</t>
+  </si>
+  <si>
+    <t>鼎通科技</t>
+  </si>
+  <si>
+    <t>高速连接:TOP4</t>
+  </si>
+  <si>
+    <t>600110</t>
+  </si>
+  <si>
+    <t>诺德股份</t>
+  </si>
+  <si>
+    <t>铜箔</t>
+  </si>
+  <si>
+    <t>铜箔:TOP1</t>
+  </si>
+  <si>
+    <t>301217</t>
+  </si>
+  <si>
+    <t>铜冠铜箔</t>
+  </si>
+  <si>
+    <t>铜箔:TOP2</t>
+  </si>
+  <si>
+    <t>688388</t>
+  </si>
+  <si>
+    <t>嘉元科技</t>
+  </si>
+  <si>
+    <t>铜箔:TOP3</t>
+  </si>
+  <si>
+    <t>301511</t>
+  </si>
+  <si>
+    <t>德福科技</t>
+  </si>
+  <si>
+    <t>铜箔:TOP4</t>
+  </si>
+  <si>
+    <t>601208</t>
+  </si>
+  <si>
+    <t>东材科技</t>
+  </si>
+  <si>
+    <t>树脂</t>
+  </si>
+  <si>
+    <t>树脂:TOP1</t>
+  </si>
+  <si>
+    <t>605589</t>
+  </si>
+  <si>
+    <t>圣泉集团</t>
+  </si>
+  <si>
+    <t>树脂:TOP2</t>
+  </si>
+  <si>
+    <t>300586</t>
+  </si>
+  <si>
+    <t>美联新材</t>
+  </si>
+  <si>
+    <t>树脂:TOP3</t>
+  </si>
+  <si>
+    <t>603002</t>
+  </si>
+  <si>
+    <t>宏昌电子</t>
+  </si>
+  <si>
+    <t>树脂:TOP4</t>
+  </si>
+  <si>
+    <t>603256</t>
+  </si>
+  <si>
+    <t>宏和科技</t>
+  </si>
+  <si>
+    <t>电子布</t>
+  </si>
+  <si>
+    <t>电子布:TOP1</t>
+  </si>
+  <si>
+    <t>600176</t>
+  </si>
+  <si>
+    <t>中国巨石</t>
+  </si>
+  <si>
+    <t>电子布:TOP2</t>
+  </si>
+  <si>
+    <t>002080</t>
+  </si>
+  <si>
+    <t>中材科技</t>
+  </si>
+  <si>
+    <t>电子布:TOP3</t>
+  </si>
+  <si>
+    <t>301526</t>
+  </si>
+  <si>
+    <t>国际复材</t>
+  </si>
+  <si>
+    <t>电子布:TOP4</t>
+  </si>
+  <si>
+    <t>002837</t>
+  </si>
+  <si>
+    <t>英维克</t>
   </si>
   <si>
     <t>液冷</t>
   </si>
   <si>
+    <t>液冷:TOP1</t>
+  </si>
+  <si>
+    <t>300499</t>
+  </si>
+  <si>
+    <t>高澜股份</t>
+  </si>
+  <si>
+    <t>液冷:TOP2</t>
+  </si>
+  <si>
+    <t>301018</t>
+  </si>
+  <si>
     <t>申菱环境</t>
   </si>
   <si>
-    <t>301018</t>
-  </si>
-  <si>
-    <t>高澜股份</t>
-  </si>
-  <si>
-    <t>300499</t>
+    <t>液冷:TOP4</t>
+  </si>
+  <si>
+    <t>002364</t>
+  </si>
+  <si>
+    <t>中恒电气</t>
+  </si>
+  <si>
+    <t>电源</t>
+  </si>
+  <si>
+    <t>电源:TOP1</t>
+  </si>
+  <si>
+    <t>002580</t>
+  </si>
+  <si>
+    <t>圣阳股份</t>
+  </si>
+  <si>
+    <t>电源:TOP2</t>
+  </si>
+  <si>
+    <t>300870</t>
+  </si>
+  <si>
+    <t>欧陆通</t>
+  </si>
+  <si>
+    <t>电源:TOP3</t>
+  </si>
+  <si>
+    <t>002851</t>
+  </si>
+  <si>
+    <t>麦格米特</t>
+  </si>
+  <si>
+    <t>电源:TOP4</t>
+  </si>
+  <si>
+    <t>002353</t>
+  </si>
+  <si>
+    <t>杰瑞股份</t>
+  </si>
+  <si>
+    <t>燃气轮机</t>
+  </si>
+  <si>
+    <t>燃气轮机:TOP1</t>
+  </si>
+  <si>
+    <t>605060</t>
+  </si>
+  <si>
+    <t>联德股份</t>
+  </si>
+  <si>
+    <t>燃气轮机:TOP2</t>
+  </si>
+  <si>
+    <t>603308</t>
+  </si>
+  <si>
+    <t>应流股份</t>
+  </si>
+  <si>
+    <t>燃气轮机:TOP3</t>
+  </si>
+  <si>
+    <t>600875</t>
+  </si>
+  <si>
+    <t>东方电气</t>
+  </si>
+  <si>
+    <t>燃气轮机:TOP4</t>
+  </si>
+  <si>
+    <t>601126</t>
+  </si>
+  <si>
+    <t>四方股份</t>
+  </si>
+  <si>
+    <t>固态变压器</t>
+  </si>
+  <si>
+    <t>固态变压器:TOP1</t>
+  </si>
+  <si>
+    <t>601179</t>
+  </si>
+  <si>
+    <t>中国西电</t>
+  </si>
+  <si>
+    <t>固态变压器:TOP2</t>
+  </si>
+  <si>
+    <t>002922</t>
+  </si>
+  <si>
+    <t>伊戈尔</t>
+  </si>
+  <si>
+    <t>固态变压器:TOP3</t>
+  </si>
+  <si>
+    <t>688676</t>
+  </si>
+  <si>
+    <t>金盘科技</t>
+  </si>
+  <si>
+    <t>固态变压器:TOP4</t>
+  </si>
+  <si>
+    <t>300442</t>
+  </si>
+  <si>
+    <t>润泽科技</t>
+  </si>
+  <si>
+    <t>AIDC</t>
+  </si>
+  <si>
+    <t>AIDC:TOP1</t>
+  </si>
+  <si>
+    <t>300017</t>
+  </si>
+  <si>
+    <t>网宿科技</t>
+  </si>
+  <si>
+    <t>AIDC:TOP2</t>
+  </si>
+  <si>
+    <t>300383</t>
+  </si>
+  <si>
+    <t>光环新网</t>
+  </si>
+  <si>
+    <t>AIDC:TOP3</t>
+  </si>
+  <si>
+    <t>603881</t>
   </si>
   <si>
     <t>数据港</t>
   </si>
   <si>
-    <t>603881</t>
-  </si>
-  <si>
-    <t>数据中心</t>
-  </si>
-  <si>
-    <t>西测测试</t>
-  </si>
-  <si>
-    <t>301306</t>
-  </si>
-  <si>
-    <t>商业航天</t>
-  </si>
-  <si>
-    <t>信维通信</t>
-  </si>
-  <si>
-    <t>300136</t>
+    <t>AIDC:TOP4</t>
+  </si>
+  <si>
+    <t>001896</t>
+  </si>
+  <si>
+    <t>豫能控股</t>
+  </si>
+  <si>
+    <t>算电协同</t>
+  </si>
+  <si>
+    <t>算电协同:TOP1</t>
+  </si>
+  <si>
+    <t>002015</t>
+  </si>
+  <si>
+    <t>协鑫能科</t>
+  </si>
+  <si>
+    <t>算电协同:TOP2</t>
+  </si>
+  <si>
+    <t>301638</t>
+  </si>
+  <si>
+    <t>南网数字</t>
+  </si>
+  <si>
+    <t>算电协同:TOP3</t>
+  </si>
+  <si>
+    <t>000601</t>
+  </si>
+  <si>
+    <t>韶能股份</t>
+  </si>
+  <si>
+    <t>算电协同:TOP4</t>
+  </si>
+  <si>
+    <t>603629</t>
+  </si>
+  <si>
+    <t>利通电子</t>
+  </si>
+  <si>
+    <t>算力租赁</t>
+  </si>
+  <si>
+    <t>算力租赁:TOP1</t>
+  </si>
+  <si>
+    <t>300857</t>
+  </si>
+  <si>
+    <t>协创数据</t>
+  </si>
+  <si>
+    <t>算力租赁:TOP2</t>
+  </si>
+  <si>
+    <t>301396</t>
+  </si>
+  <si>
+    <t>宏景科技</t>
+  </si>
+  <si>
+    <t>算力租赁:TOP3</t>
+  </si>
+  <si>
+    <t>688158</t>
+  </si>
+  <si>
+    <t>优刻得-W</t>
+  </si>
+  <si>
+    <t>算力租赁:TOP4</t>
+  </si>
+  <si>
+    <t>manual:AI算力产业链; 原表:优刻得</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="000000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -126,7 +871,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -134,14 +879,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -149,7 +894,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -157,7 +902,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -165,7 +910,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -173,7 +918,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -181,14 +926,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -196,7 +941,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -204,7 +949,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -212,14 +957,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -227,42 +972,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -461,12 +1206,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -568,32 +1328,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -602,130 +1353,142 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -775,6 +1538,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1000,9 +1764,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1010,109 +1774,49 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="ChatGPT">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1121,80 +1825,85 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1212,22 +1921,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1249,125 +1958,1859 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:G80"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.6153846153846" customWidth="1"/>
-    <col min="2" max="2" width="13.1346153846154" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="8.77941176470588" customWidth="1"/>
+    <col min="3" max="4" width="11.5588235294118" customWidth="1"/>
+    <col min="5" max="5" width="13.9705882352941" customWidth="1"/>
+    <col min="6" max="6" width="20.2205882352941" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" ht="34" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5">
+        <v>90</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>85</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
+        <v>80</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="C5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>75</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5">
+        <v>90</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>22</v>
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="5">
+        <v>85</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5">
+        <v>80</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="5">
+        <v>75</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5">
+        <v>90</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="5">
+        <v>85</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="5">
+        <v>80</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="5">
+        <v>75</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="5">
+        <v>90</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="5">
+        <v>85</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="5">
+        <v>80</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="5">
+        <v>75</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="5">
+        <v>90</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="5">
+        <v>85</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="5">
+        <v>80</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="5">
+        <v>80</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="5">
+        <v>90</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="5">
+        <v>85</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="5">
+        <v>80</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="5">
+        <v>75</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="5">
+        <v>90</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="5">
+        <v>85</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="5">
+        <v>80</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="5">
+        <v>75</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="5">
+        <v>90</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="5">
+        <v>85</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="5">
+        <v>80</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="5">
+        <v>75</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="5">
+        <v>90</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="5">
+        <v>85</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" s="5">
+        <v>80</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="5">
+        <v>75</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="5">
+        <v>90</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="5">
+        <v>85</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="5">
+        <v>80</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="5">
+        <v>75</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="5">
+        <v>90</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="5">
+        <v>85</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="5">
+        <v>80</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E45" s="5">
+        <v>75</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46" s="5">
+        <v>90</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="5">
+        <v>85</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="5">
+        <v>80</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E49" s="5">
+        <v>75</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="5">
+        <v>90</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="5">
+        <v>85</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52" s="5">
+        <v>80</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E53" s="5">
+        <v>75</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E54" s="5">
+        <v>90</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E55" s="5">
+        <v>85</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E56" s="5">
+        <v>75</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E57" s="5">
+        <v>90</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E58" s="5">
+        <v>85</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E59" s="5">
+        <v>80</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" s="5">
+        <v>75</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" s="5">
+        <v>90</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E62" s="5">
+        <v>85</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E63" s="5">
+        <v>80</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" s="5">
+        <v>75</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E65" s="5">
+        <v>90</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E66" s="5">
+        <v>85</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E67" s="5">
+        <v>80</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E68" s="5">
+        <v>75</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E69" s="5">
+        <v>90</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E70" s="5">
+        <v>85</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E71" s="5">
+        <v>80</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E72" s="5">
+        <v>75</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E73" s="5">
+        <v>90</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" s="5">
+        <v>85</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E75" s="5">
+        <v>80</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E76" s="5">
+        <v>75</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E77" s="5">
+        <v>90</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E78" s="5">
+        <v>85</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E79" s="5">
+        <v>80</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E80" s="5">
+        <v>75</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>